--- a/ci-cd-merge-resolver/repoCollector/datasets/guacamole-client.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/guacamole-client.xlsx
@@ -44,6 +44,15 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>494c4ce05ad187b4640461e16d52acb147cfb819</t>
+  </si>
+  <si>
+    <t>b5c9a08e598f66d4196c8a941a0d0dc026aca6fe</t>
+  </si>
+  <si>
+    <t>1ae04849f90bb7214b153e21337e573318c47dba</t>
+  </si>
+  <si>
     <t>1f8947164a4ed28784f1be470a68afdba1427f82</t>
   </si>
   <si>
@@ -51,15 +60,6 @@
   </si>
   <si>
     <t>4fde5adccbdcb476d4124d36a43179fa48591b1d</t>
-  </si>
-  <si>
-    <t>494c4ce05ad187b4640461e16d52acb147cfb819</t>
-  </si>
-  <si>
-    <t>b5c9a08e598f66d4196c8a941a0d0dc026aca6fe</t>
-  </si>
-  <si>
-    <t>1ae04849f90bb7214b153e21337e573318c47dba</t>
   </si>
   <si>
     <t>2bf93c1305caaeba1f15a076f84360e6c273e13b</t>
@@ -162,10 +162,10 @@
         <v>35.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -174,10 +174,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.17000001668930054</v>
+        <v>0.05700000002980232</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -191,13 +191,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>14.0</v>
+        <v>35.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -206,10 +206,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.08899999409914017</v>
+        <v>0.1340000033378601</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -238,10 +238,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.1549999862909317</v>
+        <v>0.05999999865889549</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
